--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156200</v>
+        <v>123178201</v>
       </c>
       <c r="B2" t="n">
         <v>103891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518621</v>
+        <v>518644</v>
       </c>
       <c r="R2" t="n">
-        <v>6467088</v>
+        <v>6467063</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -775,10 +775,232 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123178203</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103891</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hagalund, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>518604</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6467121</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, innerslänt</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Melina Eberhagen</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123156200</v>
+      </c>
+      <c r="B4" t="n">
+        <v>103891</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hagalund, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>518621</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6467088</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Östra vägsidan, ytterslänt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Melina Eberhagen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178201</v>
+        <v>123178203</v>
       </c>
       <c r="B2" t="n">
         <v>103891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518644</v>
+        <v>518604</v>
       </c>
       <c r="R2" t="n">
-        <v>6467063</v>
+        <v>6467121</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178203</v>
+        <v>123178201</v>
       </c>
       <c r="B3" t="n">
         <v>103891</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518604</v>
+        <v>518644</v>
       </c>
       <c r="R3" t="n">
-        <v>6467121</v>
+        <v>6467063</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178203</v>
+        <v>123178201</v>
       </c>
       <c r="B2" t="n">
         <v>103891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518604</v>
+        <v>518644</v>
       </c>
       <c r="R2" t="n">
-        <v>6467121</v>
+        <v>6467063</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178201</v>
+        <v>123178203</v>
       </c>
       <c r="B3" t="n">
         <v>103891</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518644</v>
+        <v>518604</v>
       </c>
       <c r="R3" t="n">
-        <v>6467063</v>
+        <v>6467121</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178201</v>
+        <v>123178203</v>
       </c>
       <c r="B2" t="n">
-        <v>103891</v>
+        <v>103894</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518644</v>
+        <v>518604</v>
       </c>
       <c r="R2" t="n">
-        <v>6467063</v>
+        <v>6467121</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178203</v>
+        <v>123178201</v>
       </c>
       <c r="B3" t="n">
-        <v>103891</v>
+        <v>103894</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518604</v>
+        <v>518644</v>
       </c>
       <c r="R3" t="n">
-        <v>6467121</v>
+        <v>6467063</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +900,7 @@
         <v>123156200</v>
       </c>
       <c r="B4" t="n">
-        <v>103891</v>
+        <v>103894</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123178203</v>
       </c>
       <c r="B2" t="n">
-        <v>103894</v>
+        <v>103896</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>123178201</v>
       </c>
       <c r="B3" t="n">
-        <v>103894</v>
+        <v>103896</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>123156200</v>
       </c>
       <c r="B4" t="n">
-        <v>103894</v>
+        <v>103896</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123178203</v>
       </c>
       <c r="B2" t="n">
-        <v>103896</v>
+        <v>103902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>123178201</v>
       </c>
       <c r="B3" t="n">
-        <v>103896</v>
+        <v>103902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>123156200</v>
       </c>
       <c r="B4" t="n">
-        <v>103896</v>
+        <v>103902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156200</v>
+        <v>123178201</v>
       </c>
       <c r="B2" t="n">
-        <v>103905</v>
+        <v>103922</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518621</v>
+        <v>518644</v>
       </c>
       <c r="R2" t="n">
-        <v>6467088</v>
+        <v>6467063</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>123178203</v>
       </c>
       <c r="B3" t="n">
-        <v>103905</v>
+        <v>103922</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178201</v>
+        <v>123156200</v>
       </c>
       <c r="B4" t="n">
-        <v>103905</v>
+        <v>103922</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518644</v>
+        <v>518621</v>
       </c>
       <c r="R4" t="n">
-        <v>6467063</v>
+        <v>6467088</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123178201</v>
       </c>
       <c r="B2" t="n">
-        <v>103922</v>
+        <v>103940</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178203</v>
+        <v>123156200</v>
       </c>
       <c r="B3" t="n">
-        <v>103922</v>
+        <v>103940</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518604</v>
+        <v>518621</v>
       </c>
       <c r="R3" t="n">
-        <v>6467121</v>
+        <v>6467088</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156200</v>
+        <v>123178203</v>
       </c>
       <c r="B4" t="n">
-        <v>103922</v>
+        <v>103940</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518621</v>
+        <v>518604</v>
       </c>
       <c r="R4" t="n">
-        <v>6467088</v>
+        <v>6467121</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178201</v>
+        <v>123156200</v>
       </c>
       <c r="B2" t="n">
-        <v>103940</v>
+        <v>103942</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518644</v>
+        <v>518621</v>
       </c>
       <c r="R2" t="n">
-        <v>6467063</v>
+        <v>6467088</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123156200</v>
+        <v>123178203</v>
       </c>
       <c r="B3" t="n">
-        <v>103940</v>
+        <v>103942</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518621</v>
+        <v>518604</v>
       </c>
       <c r="R3" t="n">
-        <v>6467088</v>
+        <v>6467121</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178203</v>
+        <v>123178201</v>
       </c>
       <c r="B4" t="n">
-        <v>103940</v>
+        <v>103942</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518604</v>
+        <v>518644</v>
       </c>
       <c r="R4" t="n">
-        <v>6467121</v>
+        <v>6467063</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123156200</v>
+        <v>123178201</v>
       </c>
       <c r="B2" t="n">
-        <v>103942</v>
+        <v>103517</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518621</v>
+        <v>518644</v>
       </c>
       <c r="R2" t="n">
-        <v>6467088</v>
+        <v>6467063</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +789,7 @@
         <v>123178203</v>
       </c>
       <c r="B3" t="n">
-        <v>103942</v>
+        <v>103517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123178201</v>
+        <v>123156200</v>
       </c>
       <c r="B4" t="n">
-        <v>103942</v>
+        <v>103517</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518644</v>
+        <v>518621</v>
       </c>
       <c r="R4" t="n">
-        <v>6467063</v>
+        <v>6467088</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,6 +1001,116 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128327958</v>
+      </c>
+      <c r="B5" t="n">
+        <v>103929</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>518604</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6467120</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gles förekomst, enstaka fläckarÖstraInneslänt (IS)Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>103929</v>
+        <v>103934</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>103934</v>
+        <v>104027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104027</v>
+        <v>104048</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104048</v>
+        <v>104060</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104060</v>
+        <v>104069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104069</v>
+        <v>104072</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104072</v>
+        <v>104099</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104099</v>
+        <v>104112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104112</v>
+        <v>104116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123178201</v>
+        <v>123156200</v>
       </c>
       <c r="B2" t="n">
-        <v>103517</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518644</v>
+        <v>518621</v>
       </c>
       <c r="R2" t="n">
-        <v>6467063</v>
+        <v>6467088</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123178203</v>
+        <v>123178201</v>
       </c>
       <c r="B3" t="n">
-        <v>103517</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518604</v>
+        <v>518644</v>
       </c>
       <c r="R3" t="n">
-        <v>6467121</v>
+        <v>6467063</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +856,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Östra vägsidan, innerslänt</t>
+          <t>Östra vägsidan, ytterslänt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123156200</v>
+        <v>123178203</v>
       </c>
       <c r="B4" t="n">
-        <v>103517</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -937,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518621</v>
+        <v>518604</v>
       </c>
       <c r="R4" t="n">
-        <v>6467088</v>
+        <v>6467121</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Östra vägsidan, ytterslänt</t>
+          <t>Östra vägsidan, innerslänt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +996,7 @@
         <v>128327958</v>
       </c>
       <c r="B5" t="n">
-        <v>104116</v>
+        <v>104640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 7564-2025 artfynd.xlsx
+++ b/artfynd/A 7564-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123156200</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123178201</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123178203</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128327958</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>